--- a/data/trans_orig/P16A20_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A20_2023-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2007</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408229</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>410208</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>292277</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294191</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>702443</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>704398</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>562175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>564275</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>392897</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>394929</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>957130</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>959204</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>412224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>414284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>286169</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>288056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>700351</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>702340</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>557052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>558896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>420554</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>422547</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>979534</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>981442</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1945671</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1947662</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1397753</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1399722</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3345402</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3347384</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2012</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>333027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>334975</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216261</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>218325</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>551303</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>553300</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>506555</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>508628</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>297842</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>299920</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>806470</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>808548</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>393991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>396051</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247850</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>249926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643906</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>645977</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>455175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>457117</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>288453</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>290466</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>745611</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>747583</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1694758</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1696771</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1056573</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1058637</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2753375</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2755408</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2016</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>333951</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>335947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215754</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>217593</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>551604</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>553540</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>520098</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>522165</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359619</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361569</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>881714</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>883734</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>404870</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>406976</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>302038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>303996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>708928</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>710972</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>437334</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>439273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>360777</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362767</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>800076</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>802040</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1702330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1704362</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1243977</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1245925</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2948290</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2950287</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2023</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49702</t>
+          <t>50392</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73186</t>
+          <t>74220</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55199</t>
+          <t>55991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81683</t>
+          <t>83264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>622691</t>
+          <t>623430</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>631882</t>
+          <t>631738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>602566</t>
+          <t>601532</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>626050</t>
+          <t>625360</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1229511</t>
+          <t>1227930</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1255995</t>
+          <t>1255203</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22531</t>
+          <t>22527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64359</t>
+          <t>64501</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93236</t>
+          <t>91290</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61044</t>
+          <t>62219</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109730</t>
+          <t>112674</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1170333</t>
+          <t>1170337</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1186649</t>
+          <t>1187934</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>864513</t>
+          <t>866459</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>893390</t>
+          <t>893248</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2040883</t>
+          <t>2037939</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2089569</t>
+          <t>2088394</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64101</t>
+          <t>62638</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>638180</t>
+          <t>593762</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63385</t>
+          <t>64568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>785675</t>
+          <t>712524</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>689803</t>
+          <t>688844</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>700789</t>
+          <t>700564</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>293973</t>
+          <t>338391</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>868052</t>
+          <t>869515</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>850162</t>
+          <t>923313</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1572452</t>
+          <t>1571269</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10184</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35506</t>
+          <t>34181</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70461</t>
+          <t>69451</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111850</t>
+          <t>108780</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88185</t>
+          <t>88520</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131910</t>
+          <t>130973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>891325</t>
+          <t>892650</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>916759</t>
+          <t>916647</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>979524</t>
+          <t>982594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1020913</t>
+          <t>1021923</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1886295</t>
+          <t>1887232</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1930020</t>
+          <t>1929685</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30900</t>
+          <t>31327</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62529</t>
+          <t>61801</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>288444</t>
+          <t>287815</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1032918</t>
+          <t>1179965</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>323603</t>
+          <t>322547</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1233134</t>
+          <t>1247335</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3396291</t>
+          <t>3397019</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3427920</t>
+          <t>3427493</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2624110</t>
+          <t>2477063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3368584</t>
+          <t>3369213</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5882714</t>
+          <t>5868513</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6792245</t>
+          <t>6793301</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A20_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A20_2023-Habitat-trans_orig.xlsx
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12011</t>
+          <t>12706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>60512</t>
+          <t>64868</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50392</t>
+          <t>52922</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74220</t>
+          <t>77713</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>67484</t>
+          <t>72312</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55991</t>
+          <t>60028</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83264</t>
+          <t>87042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>628469</t>
+          <t>683266</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>623430</t>
+          <t>678004</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>631738</t>
+          <t>687004</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>615240</t>
+          <t>668245</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>601532</t>
+          <t>655400</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>625360</t>
+          <t>680191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1243710</t>
+          <t>1351511</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1227930</t>
+          <t>1336781</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1255203</t>
+          <t>1363795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13061</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>7790</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22527</t>
+          <t>23389</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>77153</t>
+          <t>86081</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64501</t>
+          <t>73140</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91290</t>
+          <t>102399</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>90214</t>
+          <t>99762</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62219</t>
+          <t>84710</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112674</t>
+          <t>118079</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1179803</t>
+          <t>1035236</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1170337</t>
+          <t>1025528</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1187934</t>
+          <t>1041127</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>880596</t>
+          <t>984378</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>866459</t>
+          <t>968060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>893248</t>
+          <t>997319</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2060399</t>
+          <t>2019614</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2037939</t>
+          <t>2001297</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2088394</t>
+          <t>2034666</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957749</t>
+          <t>1070459</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957749</t>
+          <t>1070459</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957749</t>
+          <t>1070459</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150613</t>
+          <t>2119376</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150613</t>
+          <t>2119376</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150613</t>
+          <t>2119376</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14840</t>
+          <t>14304</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>258882</t>
+          <t>66362</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62638</t>
+          <t>53665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>593762</t>
+          <t>82338</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>265788</t>
+          <t>74318</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64568</t>
+          <t>60924</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>712524</t>
+          <t>90769</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>696778</t>
+          <t>794130</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>688844</t>
+          <t>787782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>700564</t>
+          <t>798898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>673271</t>
+          <t>744577</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>338391</t>
+          <t>728601</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>869515</t>
+          <t>757274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1370049</t>
+          <t>1538706</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>923313</t>
+          <t>1522255</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1571269</t>
+          <t>1552100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932153</t>
+          <t>810939</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932153</t>
+          <t>810939</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932153</t>
+          <t>810939</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1635837</t>
+          <t>1613024</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1635837</t>
+          <t>1613024</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1635837</t>
+          <t>1613024</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,22 +7598,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18184</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34181</t>
+          <t>33029</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89707</t>
+          <t>93749</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69451</t>
+          <t>79145</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108780</t>
+          <t>110369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>107891</t>
+          <t>112071</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88520</t>
+          <t>97352</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130973</t>
+          <t>132397</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -7711,27 +7711,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>908647</t>
+          <t>971740</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>892650</t>
+          <t>957033</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>916647</t>
+          <t>979213</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1001667</t>
+          <t>1023282</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>982594</t>
+          <t>1006662</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1021923</t>
+          <t>1037886</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1910314</t>
+          <t>1995022</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1887232</t>
+          <t>1974696</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1929685</t>
+          <t>2009741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>47404</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31327</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61801</t>
+          <t>63640</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>486253</t>
+          <t>311059</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>287815</t>
+          <t>283571</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1179965</t>
+          <t>344144</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>531377</t>
+          <t>358463</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>322547</t>
+          <t>327281</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1247335</t>
+          <t>389166</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3413696</t>
+          <t>3484371</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3397019</t>
+          <t>3468135</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3427493</t>
+          <t>3497563</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3170775</t>
+          <t>3420483</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2477063</t>
+          <t>3387398</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3369213</t>
+          <t>3447971</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6584471</t>
+          <t>6904853</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5868513</t>
+          <t>6874150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6793301</t>
+          <t>6936035</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3657028</t>
+          <t>3731542</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3657028</t>
+          <t>3731542</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3657028</t>
+          <t>3731542</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7115848</t>
+          <t>7263316</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7115848</t>
+          <t>7263316</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7115848</t>
+          <t>7263316</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
